--- a/بيانات_الموقع_أحلام_الجزيرة.xlsx
+++ b/بيانات_الموقع_أحلام_الجزيرة.xlsx
@@ -11,7 +11,10 @@
     <sheet name="الخدمات" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="المنتجات" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="العلامات التجارية" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="تعليمات التعبئة" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="الاعتمادات والشهادات" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="المشاريع والأعمال" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="معلومات إضافية" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="تعليمات التعبئة" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2371,7 +2374,1084 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="50" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>الاعتمادات والشهادات والتراخيص
+Credentials, Certifications &amp; Licenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>م
+#</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>نوع الوثيقة / الشهادة
+Document / Certificate Type</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>الرقم / المرجع
+Number / Reference</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>تاريخ الإصدار
+Issue Date</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>تاريخ الانتهاء
+Expiry Date</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>الجهة المصدرة
+Issuing Authority</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>هل يوجد نسخة PDF / صورة؟
+PDF / Image Available?
+(نعم/لا)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>اسم الملف
+Filename</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>ملاحظات
+Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="35" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>السجل التجاري
+Commercial Registration (CR)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>وزارة التجارة</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="35" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>شهادة ضريبة القيمة المضافة
+VAT Certificate</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>هيئة الزكاة والضريبة والجمارك</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="35" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>شهادة ISO (حدد النوع)
+ISO Certificate</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>مثال: ISO 9001</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="35" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>تصنيف المقاولين
+Contractor Classification</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>وزارة الشؤون البلدية</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>اعتماد SAMA
+SAMA Approval/Compliance</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>البنك المركزي السعودي</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="35" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>رخصة الدفاع المدني
+Civil Defense License</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9" ht="35" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>عضوية غرفة التجارة
+Chamber of Commerce Membership</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="35" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>شهادة اعتماد أخرى
+Other Certification</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11" ht="35" customHeight="1">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="35" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="35" customHeight="1">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="50" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>المشاريع المنفذة (أعمالنا)
+Completed Projects (Portfolio)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>م
+#</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>اسم المشروع
+Project Name</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>نوع العمل
+Work Type
+(تركيب/صيانة/تجهيز)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>القطاع
+Sector
+(بنوك/حكومي/تجاري)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>اسم العميل
+Client Name
+(أو 'سري')</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>المدينة
+City</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>سنة التنفيذ
+Year</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>وصف مختصر
+Brief Description
+(2-3 أسطر)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>هل يوجد صور؟
+Photos Available?
+(نعم/لا)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>عدد الصور
+# of Photos</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>هل مسموح بذكر اسم العميل؟
+Client Name Publishable?
+(نعم/لا)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>ملاحظات
+Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>تجهيز غرفة خزائن</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>بنوك</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>تركيب كاميرات مراقبة</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>تجاري</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>نقل وتركيب خزنة ثقيلة</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>بنوك</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>عقد صيانة سنوي</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>حكومي</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="50" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>معلومات إضافية مطلوبة
+Additional Information Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>م
+#</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>البند
+Item</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>الإجابة / المعلومات
+Answer / Information</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ملاحظات
+Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>سنة تأسيس الشركة
+Year of establishment</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>عدد الموظفين التقريبي
+Approximate number of employees</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>عدد المشاريع المنفذة (هل رقم +500 دقيق؟)
+Number of projects (is +500 accurate?)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>عدد سنوات الخبرة (هل رقم +15 دقيق؟)
+Years of experience (is +15 accurate?)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>عدد الفروع الفعلي (هل الرقم 6 دقيق؟)
+Number of branches (is 6 accurate?)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>هل يوجد ملف تعريفي للشركة (Company Profile PDF)؟
+Is there a company profile document?</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>هل يوجد كتالوجات منتجات PDF قابلة للتحميل؟
+Are there downloadable product catalogs (PDF)?</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>إرفاقها مع هذا الملف</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>هل يوجد شهادات أو تقييمات من عملاء يمكن نشرها؟
+Any publishable client testimonials?</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>هل شعارات العملاء الـ 15 الحالية على الموقع محدثة ودقيقة؟
+Are the 15 client logos currently on the site accurate?</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>هل هناك عملاء جدد يجب إضافتهم على الموقع؟
+Any new clients to add?</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>هل هناك وظائف شاغرة حالياً؟
+Are there current job openings?</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>إذا نعم: المسميات والمتطلبات</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>ما هي مدة الضمان على المنتجات؟
+What is the warranty period for products?</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>للأسئلة الشائعة</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>ما هي شروط عقود الصيانة الدورية؟
+What are the maintenance contract terms?</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>للأسئلة الشائعة</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>هل محتوى سياسة الخصوصية والشروط والأحكام معتمد؟
+Are the privacy policy &amp; terms approved?</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>صور من مقر الشركة / المستودعات / ورش العمل
+Photos of office / warehouse / workshop</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>لصفحة من نحن</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>قصة تأسيس الشركة (كيف بدأت ومن المؤسس)
+Company founding story</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>لصفحة من نحن</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -2484,6 +3564,61 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>الأوراق المضافة حديثاً:</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>5️⃣  الاعتمادات والشهادات – السجل التجاري، الرقم الضريبي، شهادات ISO، اعتمادات SAMA والمقاولين.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>6️⃣  المشاريع والأعمال – أبرز المشاريع المنفذة مع صور ووصف وبيانات العميل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>7️⃣  معلومات إضافية – أسئلة متفرقة حول أرقام الشركة وقصة التأسيس وتقييمات العملاء.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ ملاحظة مهمة جداً:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>• أرقام السجل التجاري والرقم الضريبي مطلوبة بشكل إلزامي على الموقع (متطلب نظامي).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>• صور المشاريع الحقيقية هي أهم عنصر لبناء الثقة مع عملاء البنوك والحكومة.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
